--- a/Excel/SceneConfig.xlsx
+++ b/Excel/SceneConfig.xlsx
@@ -1,40 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FDA188-7370-4B51-8F3A-256DB5B9FD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SceneProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>作者</author>
     <author>Administrator</author>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="O3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -43,7 +49,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -53,14 +58,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="P3" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -69,7 +73,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -78,14 +81,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="Q3" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -94,7 +96,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -105,14 +106,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="R3" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -121,7 +121,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -130,14 +129,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="X3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="X3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -146,7 +144,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -156,14 +153,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="Y3" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -172,7 +168,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -181,14 +176,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="AI3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -197,7 +191,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -205,14 +198,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="K4" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>public const int NONE = 0;
@@ -245,14 +237,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="N4" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -261,7 +252,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -275,18 +265,18 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="Item_Template" type="4" refreshedVersion="2" background="1" saveData="1">
-    <webPr xml="1" sourceData="1" parsePre="1" consecutive="1" xl2000="1" url="D:\SVN_Work\S_数据表\XML映射模版\Item_Template.xml" htmlTables="1" htmlFormat="all"/>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" name="Item_Template" type="4" background="1" refreshedVersion="2" saveData="1">
+    <webPr parsePre="1" consecutive="1" xl2000="1" sourceData="1" xml="1" url="D:\SVN_Work\S_数据表\XML映射模版\Item_Template.xml" htmlFormat="all" htmlTables="1"/>
   </connection>
-  <connection id="2" xr16:uid="{00000000-0015-0000-FFFF-FFFF01000000}" name="Item_Template1" type="4" refreshedVersion="2" background="1" saveData="1">
-    <webPr xml="1" sourceData="1" parsePre="1" consecutive="1" xl2000="1" url="D:\SVN_Work\S_数据表\XML映射模版\Item_Template.xml" htmlTables="1" htmlFormat="all"/>
+  <connection id="2" name="Item_Template1" type="4" background="1" refreshedVersion="2" saveData="1">
+    <webPr parsePre="1" consecutive="1" xl2000="1" sourceData="1" xml="1" url="D:\SVN_Work\S_数据表\XML映射模版\Item_Template.xml" htmlFormat="all" htmlTables="1"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="214">
   <si>
     <t>c</t>
   </si>
@@ -384,6 +374,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Name_EN</t>
+  </si>
+  <si>
     <t>Icon</t>
   </si>
   <si>
@@ -456,6 +449,9 @@
     <t>ChapterDes</t>
   </si>
   <si>
+    <t>ChapterDes_EN</t>
+  </si>
+  <si>
     <t>RewardShow</t>
   </si>
   <si>
@@ -486,10 +482,16 @@
     <t>主城</t>
   </si>
   <si>
+    <t>Main City</t>
+  </si>
+  <si>
     <t>-4000,-0,8,2983,10000</t>
   </si>
   <si>
-    <t>-220,-25,4000</t>
+    <t>-1000,0,0</t>
+  </si>
+  <si>
+    <t>20000001,20000002,20000003,20000004,20000006,20000009,20000010,20000011,20000012,20000013,20000014,20000015,20000016,20000017,20000018,20000019,20000020,20000021,20000022,20000023,20000024,20000025,20000026,20000027,20000028,20000029,20000030,20000031,20000032,20000033,20000036,20000037,30000011,20000039,20000040,20000041,20000042,20000043,20000044</t>
   </si>
   <si>
     <t>3</t>
@@ -507,6 +509,12 @@
     <t>绿谷村</t>
   </si>
   <si>
+    <t>Green Valley</t>
+  </si>
+  <si>
+    <t>ImgBig_13</t>
+  </si>
+  <si>
     <t>-4501,0,13033</t>
   </si>
   <si>
@@ -522,12 +530,21 @@
     <t>1;15.83,0.05,-69.15;72001003;1@1;53.82,0.05,-67.31;72001004;1@1;-43.27,0.02,101.65;72001003;1@1;-29.75,0.05,55.92;72001003;1@1;-19.51,0.02,61.98;72001002;1@1;90.89,0.06,63.31;72001013;1@1;35.00,0.08,-63.73;72001012;1@1;-24.23,0.15,6.05;72001011;1@1;-34.08,0.05,121.12;72001001;1@1;-31.42,0.03,116.10;72001001;1@1;-30.16,0.04,111.97;72001001;1@1;-28.55,0.03,106.66;72001001;1@1;-27.29,0.04,102.53;72001001;1@1;-27.80,0.04,90.87;72001001;1@1;-29.06,0.03,95.00;72001001;1@1;-41.42,0.03,93.67;72001001;1@1;-40.16,0.04,89.54;72001001;1@1;-13.78,0.03,-36.14;72001001;1@1;-12.52,0.04,-40.27;72001001;1@1;-24.60,0.04,-38.69;72001001;1@1;-25.86,0.03,-34.55;72001001;1@1;-23.05,0.04,-48.54;72001001;1@1;-24.31,0.03,-44.41;72001001;1@1;-3.99,0.04,-51.50;72001001;1@1;-8.19,0.03,-49.74;72001001;1@1;-13.84,0.04,-59.26;72001001;1@1;-18.04,0.03,-57.50;72001001;1@1;58.35,0.04,-27.84;72001001;1@1;58.47,0.03,-23.88;72001001;1@1;71.76,0.04,-28.74;72001001;1@1;71.88,0.03,-24.78;72001001;1@1;71.32,0.04,-13.76;72001001;1@1;71.44,0.03,-9.80;72001001;1@1;60.80,0.04,-14.32;72001001;1@1;60.92,0.03,-10.36;72001001;1@1;87.37,0.03,46.68;72001001;1@1;83.34,0.04,41.53;72001001;1@1;81.91,0.03,47.71;72001001;1@1;75.57,0.03,45.78;72001001;1@1;83.25,0.03,53.93;72001001;1@1;74.54,0.03,71.98;72001001;1@1;75.88,0.03,78.20;72001001;1@1;75.97,0.04,65.80;72001001;1@1;-27.64,0.02,61.98;72001002;1@1;-17.63,0.02,50.00;72001002;1@1;-25.76,0.02,50.00;72001002;1@1;-13.19,0.05,55.74;72001003;1@1;-28.97,0.05,68.46;72001001;1@1;-16.77,0.05,69.24;72001001;1@1;-25.02,0.05,81.74;72001001;1@1;-42.70,0.02,109.76;72001002;1@1;-42.21,0.02,113.21;72001002;1@1;-38.99,0.02,85.59;72001003;1@1;-32.83,0.02,73.98;72001003;1@1;-20.69,0.02,75.10;72001003;1@1;-25.80,0.02,42.21;72001002;1@1;-16.57,0.02,41.06;72001002;1@1;-16.57,0.02,37.23;72001002;1@1;-25.80,0.02,38.38;72001002;1@1;-18.17,0.02,25.93;72001002;1@1;-26.30,0.02,25.93;72001002;1@1;-26.30,0.02,22.10;72001002;1@1;-18.17,0.02,22.10;72001002;1@1;-19.56,0.02,-14.21;72001002;1@1;-27.69,0.02,-14.21;72001002;1@1;-27.69,0.02,-10.38;72001002;1@1;-19.56,0.02,-10.38;72001002;1@1;-19.56,0.02,-20.77;72001002;1@1;-27.69,0.02,-20.77;72001002;1@1;-27.69,0.02,-24.60;72001002;1@1;-19.56,0.02,-24.60;72001002;1@1;19.42,0.05,-69.15;72001003;1@1;22.84,0.05,-69.15;72001003;1@1;15.83,0.05,-55.83;72001003;1@1;19.42,0.05,-55.83;72001003;1@1;22.84,0.05,-55.83;72001003;1@1;5.96,0.05,-54.84;72001003;1@1;2.54,0.05,-54.84;72001003;1@1;3.98,0.05,-67.26;72001003;1@1;7.40,0.05,-67.26;72001003;1@1;48.98,0.05,-54.24;72001004;1@1;68.83,0.05,-59.24;72001004;1@1;70.55,0.05,-44.22;72001004;1@1;63.15,0.05,-65.04;72001004;1@1;54.28,0.05,-49.76;72001004;1@1;70.55,0.05,-51.83;72001004;1@1;57.12,0.05,-42.69;72001004;1@1;67.07,0.02,-35.95;72001002;1@1;57.23,0.02,-35.04;72001002;1@1;60.58,0.02,2.08;72001002;1@1;70.56,0.02,2.08;72001002;1@1;60.58,0.02,5.77;72001002;1@1;70.56,0.02,5.77;72001002;1@1;63.26,0.02,21.87;72001002;1@1;72.07,0.02,18.16;72001002;1@1;72.07,0.02,21.85;72001002;1@1;63.26,0.02,25.56;72001002;1@1;60.30,0.05,14.63;72001004;1@1;72.32,0.05,12.44;72001004;1@1;62.65,0.05,33.72;72001004;1@1;74.67,0.05,31.53;72001004;1@1;80.25,0.05,36.90;72001004;1@1;65.09,0.05,50.98;72001004;1@1;65.90,0.02,65.19;72001002;1@1;65.90,0.02,60.08;72001002;1@1;62.90,0.02,41.10;72001002;1@1;80.50,0.02,74.00;72001002;1@1;91.21,0.05,50.10;72001003;1@1;68.40,0.05,69.29;72001003;1@1;80.25,0.05,69.29;72001003;1</t>
   </si>
   <si>
+    <t>在人们眼中,这片区域有很深未知的东西,亲爱的冒险者,你准备好开始探险了嘛?</t>
+  </si>
+  <si>
+    <t>In people's eyes, there is something very mysterious in this area. Dear adventurer, are you ready to start the exploration?</t>
+  </si>
+  <si>
     <t>21.4,100,35.5,0,105</t>
   </si>
   <si>
     <t>荒漠领域</t>
   </si>
   <si>
+    <t>Desert Domain</t>
+  </si>
+  <si>
     <t>ImgBig_12</t>
   </si>
   <si>
@@ -552,6 +569,9 @@
     <t>冰封之地</t>
   </si>
   <si>
+    <t>Frozen Land</t>
+  </si>
+  <si>
     <t>ImgBig_14</t>
   </si>
   <si>
@@ -573,6 +593,12 @@
     <t>46.9,93.7,105,0,105</t>
   </si>
   <si>
+    <t>森林巢穴</t>
+  </si>
+  <si>
+    <t>Forest Nest</t>
+  </si>
+  <si>
     <t>ImgBig_11</t>
   </si>
   <si>
@@ -594,6 +620,12 @@
     <t>4,100,4,0,65</t>
   </si>
   <si>
+    <t>上古遗迹</t>
+  </si>
+  <si>
+    <t>Ancient Ruins</t>
+  </si>
+  <si>
     <t>ImgBig_15</t>
   </si>
   <si>
@@ -612,21 +644,54 @@
     <t>35,89,10,0,90</t>
   </si>
   <si>
+    <t>炙热熔炎</t>
+  </si>
+  <si>
+    <t>Scorching Flame</t>
+  </si>
+  <si>
     <t>ImgBig_16</t>
   </si>
   <si>
     <t>15545,2978,25967</t>
   </si>
   <si>
+    <t>69</t>
+  </si>
+  <si>
     <t>70,70</t>
   </si>
   <si>
     <t>142,89,81.8,0,190</t>
   </si>
   <si>
+    <t>冰蚀幽城</t>
+  </si>
+  <si>
+    <t>Frostveil</t>
+  </si>
+  <si>
+    <t>ImgBig_17</t>
+  </si>
+  <si>
+    <t>16059,2815,27078</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>72,72</t>
+  </si>
+  <si>
+    <t>142,89,81.8,0,230</t>
+  </si>
+  <si>
     <t>宝藏之地</t>
   </si>
   <si>
+    <t>Treasure Land</t>
+  </si>
+  <si>
     <t>-7000,100,450</t>
   </si>
   <si>
@@ -640,6 +705,9 @@
   </si>
   <si>
     <t>密境</t>
+  </si>
+  <si>
+    <t>Secret Realm</t>
   </si>
   <si>
     <t>-1145,50,-2350</t>
@@ -653,7 +721,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>4,100,4,</t>
@@ -663,7 +730,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>40</t>
@@ -673,7 +739,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>,</t>
@@ -683,7 +748,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>30</t>
@@ -693,6 +757,9 @@
     <t>挑战之地</t>
   </si>
   <si>
+    <t>Challenging Land</t>
+  </si>
+  <si>
     <t>0,0,0</t>
   </si>
   <si>
@@ -708,6 +775,9 @@
     <t>家族争霸赛地图</t>
   </si>
   <si>
+    <t>Family Fight</t>
+  </si>
+  <si>
     <t>2954,4,-223</t>
   </si>
   <si>
@@ -723,6 +793,9 @@
     <t>家族地图</t>
   </si>
   <si>
+    <t>Family Map</t>
+  </si>
+  <si>
     <t>-4190,5,-123</t>
   </si>
   <si>
@@ -735,6 +808,9 @@
     <t>竞技场</t>
   </si>
   <si>
+    <t>Arena</t>
+  </si>
+  <si>
     <t>-950,0,80</t>
   </si>
   <si>
@@ -747,6 +823,9 @@
     <t>我的家园</t>
   </si>
   <si>
+    <t>My home</t>
+  </si>
+  <si>
     <t>1188,0,-3704</t>
   </si>
   <si>
@@ -762,10 +841,19 @@
     <t>宠物天梯</t>
   </si>
   <si>
+    <t>Pet ladder</t>
+  </si>
+  <si>
     <t>宠物关卡</t>
   </si>
   <si>
+    <t>Pet Leveling Area</t>
+  </si>
+  <si>
     <t>随机关卡</t>
+  </si>
+  <si>
+    <t>Random Encounter</t>
   </si>
   <si>
     <t>22574,2903,-4850</t>
@@ -776,7 +864,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>战场(</t>
@@ -786,7 +873,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -796,7 +882,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>0</t>
@@ -806,7 +891,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>-</t>
@@ -816,11 +900,13 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>29级)</t>
     </r>
+  </si>
+  <si>
+    <t>Battlefield (Level 10 - 29)</t>
   </si>
   <si>
     <t>-8254,34,0,9990,34,0</t>
@@ -840,7 +926,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>战场(3</t>
@@ -850,7 +935,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>0-</t>
@@ -860,7 +944,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>60级</t>
@@ -870,13 +953,15 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
+    <t>Battlefield (30-60 levels)</t>
+  </si>
+  <si>
     <t>30,100</t>
   </si>
   <si>
@@ -886,9 +971,15 @@
     <t>试炼之地</t>
   </si>
   <si>
+    <t>Trial Grounds</t>
+  </si>
+  <si>
     <t>勇士角斗</t>
   </si>
   <si>
+    <t>Warrior Battle</t>
+  </si>
+  <si>
     <t>-1350,57,0</t>
   </si>
   <si>
@@ -901,192 +992,59 @@
     <t>动物奔跑大赛</t>
   </si>
   <si>
+    <t>Animal Running</t>
+  </si>
+  <si>
     <t>1270,98,-4476</t>
   </si>
   <si>
     <t>恶魔活动地图</t>
   </si>
   <si>
+    <t>Demon Activity</t>
+  </si>
+  <si>
     <t>封印之塔</t>
   </si>
   <si>
+    <t>Seal Tower</t>
+  </si>
+  <si>
     <t>喜从天降</t>
   </si>
   <si>
+    <t>A Gift from Heaven</t>
+  </si>
+  <si>
     <t>宠物矿场</t>
   </si>
   <si>
+    <t>Pet Mine</t>
+  </si>
+  <si>
     <t>赛季之塔</t>
   </si>
   <si>
+    <t>Seasonal Tower</t>
+  </si>
+  <si>
     <t>1V1挑战赛</t>
   </si>
   <si>
-    <t>Name_EN</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desert Domain</t>
-  </si>
-  <si>
-    <t>Frozen Land</t>
-  </si>
-  <si>
-    <t>Forest Nest</t>
-  </si>
-  <si>
-    <t>Ancient Ruins</t>
-  </si>
-  <si>
-    <t>Treasure Land</t>
-  </si>
-  <si>
-    <t>Secret Realm</t>
-  </si>
-  <si>
-    <t>Challenging Land</t>
-  </si>
-  <si>
-    <t>Family Map</t>
-  </si>
-  <si>
-    <t>Arena</t>
-  </si>
-  <si>
-    <t>My home</t>
-  </si>
-  <si>
-    <t>Pet ladder</t>
-  </si>
-  <si>
-    <t>Pet Leveling Area</t>
-  </si>
-  <si>
-    <t>Random Encounter</t>
-  </si>
-  <si>
-    <t>Battlefield (Level 10 - 29)</t>
-  </si>
-  <si>
-    <t>Battlefield (30-60 levels)</t>
-  </si>
-  <si>
-    <t>Trial Grounds</t>
-  </si>
-  <si>
-    <t>Warrior Battle</t>
-  </si>
-  <si>
-    <t>Seal Tower</t>
-  </si>
-  <si>
-    <t>A Gift from Heaven</t>
-  </si>
-  <si>
-    <t>Pet Mine</t>
-  </si>
-  <si>
-    <t>Seasonal Tower</t>
-  </si>
-  <si>
     <t>1v1 Challenge</t>
-  </si>
-  <si>
-    <t>Main City</t>
-  </si>
-  <si>
-    <t>ChapterDes_EN</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>In people's eyes, there is something very mysterious in this area. Dear adventurer, are you ready to start the exploration?</t>
-  </si>
-  <si>
-    <t>Green Valley</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Scorching Flame</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Animal Running</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Demon Activity</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Family Fight</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰蚀幽城</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Frostveil</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ImgBig_17</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>72</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>72,72</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>16059,2815,27078</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>69</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>142,89,81.8,0,230</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>在人们眼中,这片区域有很深未知的东西,亲爱的冒险者,你准备好开始探险了嘛?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ImgBig_13</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>20000001,20000002,20000003,20000004,20000006,20000009,20000010,20000011,20000012,20000013,20000014,20000015,20000016,20000017,20000018,20000019,20000020,20000021,20000022,20000023,20000024,20000025,20000026,20000027,20000028,20000029,20000030,20000031,20000032,20000033,20000036,20000037,30000011,20000039,20000040,20000041,20000042,20000043,20000044</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>森林巢穴</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>上古遗迹</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>炙热熔炎</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1098,7 +1056,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1106,7 +1063,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1115,14 +1071,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1130,31 +1084,165 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1181,12 +1269,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14951017792291024"/>
+        <fgColor theme="0" tint="-0.14951017792291"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1259,14 +1533,256 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1291,72 +1807,116 @@
     <xf numFmtId="49" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 5" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="常规 6" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 5" xfId="50"/>
+    <cellStyle name="常规 6" xfId="51"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1393,18 +1953,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="C4:K6" totalsRowShown="0">
-  <autoFilter ref="C4:K6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="C4:K6" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C4:K6" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Name"/>
-    <tableColumn id="8" xr3:uid="{41F534E2-D6EA-4B79-ACD6-FD4565BD72AE}" name="Name_EN"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Icon"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Icon2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="StallArea"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="InitPos"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="NpcList"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="MapType"/>
+    <tableColumn id="1" name="Id"/>
+    <tableColumn id="2" name="Name"/>
+    <tableColumn id="8" name="Name_EN"/>
+    <tableColumn id="3" name="Icon"/>
+    <tableColumn id="9" name="Icon2"/>
+    <tableColumn id="4" name="StallArea"/>
+    <tableColumn id="5" name="InitPos"/>
+    <tableColumn id="6" name="NpcList"/>
+    <tableColumn id="7" name="MapType"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1691,25 +2251,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="B2:AI37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="17.5" customWidth="1"/>
     <col min="4" max="4" width="16.125" customWidth="1"/>
-    <col min="5" max="5" width="26.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.75" customWidth="1"/>
     <col min="6" max="7" width="17.125" customWidth="1"/>
     <col min="8" max="8" width="16.75" customWidth="1"/>
     <col min="9" max="9" width="16.875" customWidth="1"/>
     <col min="10" max="10" width="31.625" customWidth="1"/>
     <col min="11" max="11" width="28.125" customWidth="1"/>
     <col min="12" max="13" width="16.75" customWidth="1"/>
-    <col min="14" max="14" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.25" customWidth="1"/>
     <col min="15" max="15" width="13.875" customWidth="1"/>
     <col min="17" max="17" width="14.875" customWidth="1"/>
     <col min="18" max="18" width="18.625" customWidth="1"/>
@@ -1727,18 +2287,18 @@
     <col min="35" max="35" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:35">
       <c r="E2" s="4" t="s">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>170</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1839,7 +2399,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1847,266 +2407,266 @@
         <v>31</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>169</v>
+        <v>32</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S4" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T4" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U4" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V4" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W4" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="X4" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y4" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Z4" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA4" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AB4" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AC4" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AD4" s="6" t="s">
-        <v>194</v>
+        <v>57</v>
       </c>
       <c r="AE4" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AF4" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AG4" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AH4" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AI4" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
-    <row r="5" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="C5" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="L5" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="M5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="O5" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="S5" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T5" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U5" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="W5" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="W5" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="X5" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Y5" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Z5" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AA5" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AB5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF5" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="AC5" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="AD5" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE5" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF5" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="AG5" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AH5" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AI5" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="6" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B6"/>
       <c r="C6" s="8">
         <v>101</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>193</v>
+        <v>68</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="L6" s="13">
+        <v>72</v>
+      </c>
+      <c r="L6" s="10">
         <v>101</v>
       </c>
-      <c r="M6" s="13">
-        <v>0</v>
-      </c>
-      <c r="N6" s="13">
-        <v>1</v>
-      </c>
-      <c r="O6" s="13">
-        <v>0</v>
-      </c>
-      <c r="P6" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>0</v>
-      </c>
-      <c r="R6" s="13">
+      <c r="M6" s="10">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10">
+        <v>1</v>
+      </c>
+      <c r="O6" s="10">
+        <v>0</v>
+      </c>
+      <c r="P6" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>0</v>
+      </c>
+      <c r="R6" s="10">
         <v>1</v>
       </c>
       <c r="S6" s="9"/>
       <c r="T6" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U6" s="13">
+        <v>73</v>
+      </c>
+      <c r="U6" s="10">
         <v>0</v>
       </c>
       <c r="V6" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="W6" s="13">
-        <v>0</v>
-      </c>
-      <c r="X6" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="13">
+        <v>74</v>
+      </c>
+      <c r="W6" s="10">
+        <v>0</v>
+      </c>
+      <c r="X6" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="10">
         <v>0</v>
       </c>
       <c r="AA6" s="9"/>
@@ -2114,42 +2674,42 @@
       <c r="AC6" s="9"/>
       <c r="AD6" s="9"/>
       <c r="AE6" s="9"/>
-      <c r="AF6" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="13">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="20" t="s">
-        <v>71</v>
+      <c r="AF6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="11" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B7"/>
       <c r="C7" s="8">
         <v>110001</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="G7" s="13">
+        <v>78</v>
+      </c>
+      <c r="G7" s="10">
         <v>110001</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="15">
+        <v>79</v>
+      </c>
+      <c r="J7" s="12"/>
+      <c r="K7" s="13">
         <v>5</v>
       </c>
       <c r="L7" s="8">
@@ -2158,89 +2718,89 @@
       <c r="M7" s="8">
         <v>110001</v>
       </c>
-      <c r="N7" s="13">
-        <v>1</v>
-      </c>
-      <c r="O7" s="13">
-        <v>0</v>
-      </c>
-      <c r="P7" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>0</v>
-      </c>
-      <c r="R7" s="13">
+      <c r="N7" s="10">
+        <v>1</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>0</v>
+      </c>
+      <c r="R7" s="10">
         <v>0</v>
       </c>
       <c r="S7" s="9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="V7" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="W7" s="13">
+        <v>82</v>
+      </c>
+      <c r="W7" s="10">
         <v>2</v>
       </c>
-      <c r="X7" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="13">
+      <c r="X7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="10">
         <v>72001013</v>
       </c>
       <c r="AA7" s="22" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AB7" s="9"/>
       <c r="AC7" s="9" t="s">
-        <v>209</v>
+        <v>84</v>
       </c>
       <c r="AD7" s="9" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="AE7" s="9"/>
-      <c r="AF7" s="13">
+      <c r="AF7" s="10">
         <v>28000</v>
       </c>
-      <c r="AG7" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="13">
+      <c r="AG7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="10">
         <v>601500201</v>
       </c>
-      <c r="AI7" s="20" t="s">
-        <v>78</v>
+      <c r="AI7" s="11" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="8" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B8"/>
       <c r="C8" s="8">
         <v>110002</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>171</v>
+        <v>88</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="G8" s="13">
+        <v>89</v>
+      </c>
+      <c r="G8" s="10">
         <v>110002</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="22" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8">
@@ -2252,89 +2812,89 @@
       <c r="M8" s="8">
         <v>110002</v>
       </c>
-      <c r="N8" s="13">
-        <v>1</v>
-      </c>
-      <c r="O8" s="13">
-        <v>0</v>
-      </c>
-      <c r="P8" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>0</v>
-      </c>
-      <c r="R8" s="13">
+      <c r="N8" s="10">
+        <v>1</v>
+      </c>
+      <c r="O8" s="10">
+        <v>0</v>
+      </c>
+      <c r="P8" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>0</v>
+      </c>
+      <c r="R8" s="10">
         <v>0</v>
       </c>
       <c r="S8" s="9" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="V8" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="W8" s="13">
+        <v>93</v>
+      </c>
+      <c r="W8" s="10">
         <v>2</v>
       </c>
-      <c r="X8" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="13">
+      <c r="X8" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="10">
         <v>72002013</v>
       </c>
       <c r="AA8" s="22" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="AB8" s="9"/>
       <c r="AC8" s="9" t="s">
-        <v>209</v>
+        <v>84</v>
       </c>
       <c r="AD8" s="9" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="AE8" s="9"/>
-      <c r="AF8" s="13">
+      <c r="AF8" s="10">
         <v>58000</v>
       </c>
-      <c r="AG8" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="13">
+      <c r="AG8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="10">
         <v>601500301</v>
       </c>
-      <c r="AI8" s="20" t="s">
-        <v>86</v>
+      <c r="AI8" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B9"/>
       <c r="C9" s="8">
         <v>110003</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>172</v>
+        <v>97</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="13">
+        <v>98</v>
+      </c>
+      <c r="G9" s="10">
         <v>110003</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="22" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="8">
@@ -2346,92 +2906,92 @@
       <c r="M9" s="8">
         <v>110003</v>
       </c>
-      <c r="N9" s="13">
-        <v>1</v>
-      </c>
-      <c r="O9" s="13">
-        <v>0</v>
-      </c>
-      <c r="P9" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>0</v>
-      </c>
-      <c r="R9" s="13">
+      <c r="N9" s="10">
+        <v>1</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0</v>
+      </c>
+      <c r="P9" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>0</v>
+      </c>
+      <c r="R9" s="10">
         <v>0</v>
       </c>
       <c r="S9" s="9" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="V9" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="W9" s="13">
+        <v>102</v>
+      </c>
+      <c r="W9" s="10">
         <v>2</v>
       </c>
-      <c r="X9" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="13">
+      <c r="X9" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="10">
         <v>72003013</v>
       </c>
       <c r="AA9" s="22" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="AB9" s="9"/>
       <c r="AC9" s="9" t="s">
-        <v>209</v>
+        <v>84</v>
       </c>
       <c r="AD9" s="9" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="AE9" s="9"/>
-      <c r="AF9" s="13">
+      <c r="AF9" s="10">
         <v>88000</v>
       </c>
-      <c r="AG9" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="13">
+      <c r="AG9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="10">
         <v>601500401</v>
       </c>
-      <c r="AI9" s="20" t="s">
-        <v>94</v>
+      <c r="AI9" s="11" t="s">
+        <v>104</v>
       </c>
     </row>
-    <row r="10" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B10"/>
       <c r="C10" s="8">
         <v>110004</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>212</v>
+        <v>105</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" s="13">
+        <v>107</v>
+      </c>
+      <c r="G10" s="10">
         <v>110004</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="J10" s="14"/>
-      <c r="K10" s="15">
+        <v>108</v>
+      </c>
+      <c r="J10" s="12"/>
+      <c r="K10" s="13">
         <v>5</v>
       </c>
       <c r="L10" s="8">
@@ -2440,92 +3000,92 @@
       <c r="M10" s="8">
         <v>110004</v>
       </c>
-      <c r="N10" s="13">
-        <v>1</v>
-      </c>
-      <c r="O10" s="13">
-        <v>0</v>
-      </c>
-      <c r="P10" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>0</v>
-      </c>
-      <c r="R10" s="13">
+      <c r="N10" s="10">
+        <v>1</v>
+      </c>
+      <c r="O10" s="10">
+        <v>0</v>
+      </c>
+      <c r="P10" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>0</v>
+      </c>
+      <c r="R10" s="10">
         <v>0</v>
       </c>
       <c r="S10" s="9" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="U10" s="9" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="V10" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="W10" s="13">
+        <v>111</v>
+      </c>
+      <c r="W10" s="10">
         <v>2</v>
       </c>
-      <c r="X10" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="13">
+      <c r="X10" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="10">
         <v>72004013</v>
       </c>
       <c r="AA10" s="22" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="AB10" s="9"/>
       <c r="AC10" s="9" t="s">
-        <v>209</v>
+        <v>84</v>
       </c>
       <c r="AD10" s="9" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="AE10" s="9"/>
-      <c r="AF10" s="13">
+      <c r="AF10" s="10">
         <v>118000</v>
       </c>
-      <c r="AG10" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="13">
+      <c r="AG10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="10">
         <v>601500501</v>
       </c>
-      <c r="AI10" s="20" t="s">
-        <v>101</v>
+      <c r="AI10" s="11" t="s">
+        <v>113</v>
       </c>
     </row>
-    <row r="11" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B11"/>
       <c r="C11" s="8">
         <v>110005</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>213</v>
+        <v>114</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="G11" s="13">
+        <v>116</v>
+      </c>
+      <c r="G11" s="10">
         <v>110005</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="J11" s="14"/>
-      <c r="K11" s="15">
+        <v>117</v>
+      </c>
+      <c r="J11" s="12"/>
+      <c r="K11" s="13">
         <v>5</v>
       </c>
       <c r="L11" s="8">
@@ -2534,92 +3094,92 @@
       <c r="M11" s="8">
         <v>110005</v>
       </c>
-      <c r="N11" s="13">
-        <v>1</v>
-      </c>
-      <c r="O11" s="13">
-        <v>0</v>
-      </c>
-      <c r="P11" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>0</v>
-      </c>
-      <c r="R11" s="13">
+      <c r="N11" s="10">
+        <v>1</v>
+      </c>
+      <c r="O11" s="10">
+        <v>0</v>
+      </c>
+      <c r="P11" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>0</v>
+      </c>
+      <c r="R11" s="10">
         <v>0</v>
       </c>
       <c r="S11" s="9" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="W11" s="13">
+        <v>120</v>
+      </c>
+      <c r="W11" s="10">
         <v>2</v>
       </c>
-      <c r="X11" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="13">
+      <c r="X11" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="10">
         <v>72005013</v>
       </c>
       <c r="AA11" s="9"/>
-      <c r="AB11" s="13">
+      <c r="AB11" s="10">
         <v>40001</v>
       </c>
       <c r="AC11" s="9" t="s">
-        <v>209</v>
+        <v>84</v>
       </c>
       <c r="AD11" s="9" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="AE11" s="9"/>
-      <c r="AF11" s="13">
+      <c r="AF11" s="10">
         <v>158000</v>
       </c>
-      <c r="AG11" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="13">
+      <c r="AG11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="10">
         <v>601500501</v>
       </c>
-      <c r="AI11" s="20" t="s">
-        <v>107</v>
+      <c r="AI11" s="11" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="12" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B12"/>
       <c r="C12" s="8">
         <v>110006</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>214</v>
+        <v>122</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>197</v>
+        <v>123</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="G12" s="13">
+        <v>124</v>
+      </c>
+      <c r="G12" s="10">
         <v>110006</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="15">
+        <v>125</v>
+      </c>
+      <c r="J12" s="12"/>
+      <c r="K12" s="13">
         <v>5</v>
       </c>
       <c r="L12" s="8">
@@ -2628,92 +3188,92 @@
       <c r="M12" s="8">
         <v>110006</v>
       </c>
-      <c r="N12" s="13">
-        <v>1</v>
-      </c>
-      <c r="O12" s="13">
-        <v>0</v>
-      </c>
-      <c r="P12" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>0</v>
-      </c>
-      <c r="R12" s="13">
+      <c r="N12" s="10">
+        <v>1</v>
+      </c>
+      <c r="O12" s="10">
+        <v>0</v>
+      </c>
+      <c r="P12" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>0</v>
+      </c>
+      <c r="R12" s="10">
         <v>0</v>
       </c>
       <c r="S12" s="9" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>207</v>
+        <v>126</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>207</v>
+        <v>126</v>
       </c>
       <c r="V12" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="W12" s="13">
+        <v>127</v>
+      </c>
+      <c r="W12" s="10">
         <v>2</v>
       </c>
-      <c r="X12" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="13">
+      <c r="X12" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="10">
         <v>72006013</v>
       </c>
       <c r="AA12" s="9"/>
-      <c r="AB12" s="13">
+      <c r="AB12" s="10">
         <v>41001</v>
       </c>
       <c r="AC12" s="9" t="s">
-        <v>209</v>
+        <v>84</v>
       </c>
       <c r="AD12" s="9" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="AE12" s="9"/>
-      <c r="AF12" s="13">
+      <c r="AF12" s="10">
         <v>206000</v>
       </c>
-      <c r="AG12" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="13">
+      <c r="AG12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="10">
         <v>601500501</v>
       </c>
-      <c r="AI12" s="20" t="s">
-        <v>111</v>
+      <c r="AI12" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="13" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B13"/>
       <c r="C13" s="8">
         <v>110007</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>201</v>
+        <v>129</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="G13" s="13">
+        <v>131</v>
+      </c>
+      <c r="G13" s="10">
         <v>110007</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="J13" s="14"/>
-      <c r="K13" s="15">
+        <v>132</v>
+      </c>
+      <c r="J13" s="12"/>
+      <c r="K13" s="13">
         <v>5</v>
       </c>
       <c r="L13" s="8">
@@ -2722,85 +3282,85 @@
       <c r="M13" s="8">
         <v>110007</v>
       </c>
-      <c r="N13" s="13">
-        <v>1</v>
-      </c>
-      <c r="O13" s="13">
-        <v>0</v>
-      </c>
-      <c r="P13" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>0</v>
-      </c>
-      <c r="R13" s="13">
+      <c r="N13" s="10">
+        <v>1</v>
+      </c>
+      <c r="O13" s="10">
+        <v>0</v>
+      </c>
+      <c r="P13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>0</v>
+      </c>
+      <c r="R13" s="10">
         <v>0</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="V13" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="W13" s="13">
+        <v>134</v>
+      </c>
+      <c r="W13" s="10">
         <v>2</v>
       </c>
-      <c r="X13" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="13">
+      <c r="X13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="10">
         <v>72007013</v>
       </c>
       <c r="AA13" s="9"/>
-      <c r="AB13" s="13">
+      <c r="AB13" s="10">
         <v>42001</v>
       </c>
       <c r="AC13" s="9" t="s">
-        <v>209</v>
+        <v>84</v>
       </c>
       <c r="AD13" s="9" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="AE13" s="9"/>
-      <c r="AF13" s="13">
+      <c r="AF13" s="10">
         <v>206000</v>
       </c>
-      <c r="AG13" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="13">
+      <c r="AG13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="10">
         <v>601500501</v>
       </c>
-      <c r="AI13" s="20" t="s">
-        <v>208</v>
+      <c r="AI13" s="11" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="14" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B14"/>
       <c r="C14" s="8">
         <v>2000001</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="22" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8">
@@ -2809,74 +3369,74 @@
       <c r="L14" s="8">
         <v>2000001</v>
       </c>
-      <c r="M14" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="N14" s="13">
-        <v>1</v>
-      </c>
-      <c r="O14" s="13">
-        <v>0</v>
-      </c>
-      <c r="P14" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>0</v>
-      </c>
-      <c r="R14" s="13">
+      <c r="M14" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="N14" s="10">
+        <v>1</v>
+      </c>
+      <c r="O14" s="10">
+        <v>0</v>
+      </c>
+      <c r="P14" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>0</v>
+      </c>
+      <c r="R14" s="10">
         <v>1</v>
       </c>
       <c r="S14" s="9" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U14" s="13">
+        <v>73</v>
+      </c>
+      <c r="U14" s="10">
         <v>1</v>
       </c>
       <c r="V14" s="9"/>
-      <c r="W14" s="13">
+      <c r="W14" s="10">
         <v>300</v>
       </c>
-      <c r="X14" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="13"/>
-      <c r="AA14" s="19" t="s">
-        <v>115</v>
+      <c r="X14" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="10"/>
+      <c r="AA14" s="15" t="s">
+        <v>140</v>
       </c>
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="9"/>
       <c r="AE14" s="9"/>
-      <c r="AF14" s="13"/>
-      <c r="AG14" s="13"/>
-      <c r="AH14" s="13"/>
+      <c r="AF14" s="10"/>
+      <c r="AG14" s="10"/>
+      <c r="AH14" s="10"/>
       <c r="AI14" s="23" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
     </row>
-    <row r="15" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B15"/>
       <c r="C15" s="8">
         <v>2000002</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="22" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8">
@@ -2885,72 +3445,72 @@
       <c r="L15" s="8">
         <v>2000002</v>
       </c>
-      <c r="M15" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="N15" s="13">
-        <v>1</v>
-      </c>
-      <c r="O15" s="13">
-        <v>0</v>
-      </c>
-      <c r="P15" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>0</v>
-      </c>
-      <c r="R15" s="13">
+      <c r="M15" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="N15" s="10">
+        <v>1</v>
+      </c>
+      <c r="O15" s="10">
+        <v>0</v>
+      </c>
+      <c r="P15" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>0</v>
+      </c>
+      <c r="R15" s="10">
         <v>1</v>
       </c>
       <c r="S15" s="9" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U15" s="13">
+        <v>73</v>
+      </c>
+      <c r="U15" s="10">
         <v>1</v>
       </c>
       <c r="V15" s="9"/>
-      <c r="W15" s="13">
+      <c r="W15" s="10">
         <v>200</v>
       </c>
-      <c r="X15" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="13"/>
+      <c r="X15" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="10"/>
       <c r="AA15" s="8"/>
-      <c r="AB15" s="13"/>
+      <c r="AB15" s="10"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="9"/>
       <c r="AE15" s="9"/>
-      <c r="AF15" s="13"/>
-      <c r="AG15" s="13"/>
-      <c r="AH15" s="13"/>
-      <c r="AI15" s="20" t="s">
-        <v>120</v>
+      <c r="AF15" s="10"/>
+      <c r="AG15" s="10"/>
+      <c r="AH15" s="10"/>
+      <c r="AI15" s="11" t="s">
+        <v>146</v>
       </c>
     </row>
-    <row r="16" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B16"/>
       <c r="C16" s="8">
         <v>2000003</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="22" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8">
@@ -2959,70 +3519,70 @@
       <c r="L16" s="8">
         <v>2000003</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="14">
         <v>2000003</v>
       </c>
-      <c r="N16" s="13">
-        <v>0</v>
-      </c>
-      <c r="O16" s="13">
-        <v>1</v>
-      </c>
-      <c r="P16" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="13">
-        <v>1</v>
-      </c>
-      <c r="R16" s="13">
+      <c r="N16" s="10">
+        <v>0</v>
+      </c>
+      <c r="O16" s="10">
+        <v>1</v>
+      </c>
+      <c r="P16" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>1</v>
+      </c>
+      <c r="R16" s="10">
         <v>1</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U16" s="13">
+        <v>73</v>
+      </c>
+      <c r="U16" s="10">
         <v>1</v>
       </c>
       <c r="V16" s="9"/>
-      <c r="W16" s="13">
-        <v>0</v>
-      </c>
-      <c r="X16" s="13">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="13"/>
+      <c r="W16" s="10">
+        <v>0</v>
+      </c>
+      <c r="X16" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="10"/>
       <c r="AA16" s="8"/>
-      <c r="AB16" s="13"/>
+      <c r="AB16" s="10"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="9"/>
       <c r="AE16" s="9"/>
-      <c r="AF16" s="13"/>
-      <c r="AG16" s="13"/>
-      <c r="AH16" s="13"/>
-      <c r="AI16" s="20"/>
+      <c r="AF16" s="10"/>
+      <c r="AG16" s="10"/>
+      <c r="AH16" s="10"/>
+      <c r="AI16" s="11"/>
     </row>
-    <row r="17" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B17"/>
       <c r="C17" s="8">
         <v>2000004</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="22" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8">
@@ -3031,71 +3591,71 @@
       <c r="L17" s="8">
         <v>2000003</v>
       </c>
-      <c r="M17" s="16">
+      <c r="M17" s="14">
         <v>2000003</v>
       </c>
-      <c r="N17" s="13">
-        <v>0</v>
-      </c>
-      <c r="O17" s="13">
-        <v>1</v>
-      </c>
-      <c r="P17" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="13">
-        <v>1</v>
-      </c>
-      <c r="R17" s="13">
+      <c r="N17" s="10">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10">
+        <v>1</v>
+      </c>
+      <c r="P17" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>1</v>
+      </c>
+      <c r="R17" s="10">
         <v>1</v>
       </c>
       <c r="S17" s="9" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U17" s="13">
+        <v>73</v>
+      </c>
+      <c r="U17" s="10">
         <v>1</v>
       </c>
       <c r="V17" s="9"/>
-      <c r="W17" s="13">
-        <v>1</v>
-      </c>
-      <c r="X17" s="13">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="13"/>
+      <c r="W17" s="10">
+        <v>1</v>
+      </c>
+      <c r="X17" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="10"/>
       <c r="AA17" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="AB17" s="13"/>
+        <v>152</v>
+      </c>
+      <c r="AB17" s="10"/>
       <c r="AC17" s="9"/>
       <c r="AD17" s="9"/>
       <c r="AE17" s="9"/>
-      <c r="AF17" s="13"/>
-      <c r="AG17" s="13"/>
-      <c r="AH17" s="13"/>
-      <c r="AI17" s="20"/>
+      <c r="AF17" s="10"/>
+      <c r="AG17" s="10"/>
+      <c r="AH17" s="10"/>
+      <c r="AI17" s="11"/>
     </row>
-    <row r="18" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" ht="20.1" customHeight="1" spans="2:35">
       <c r="C18" s="8">
         <v>2000008</v>
       </c>
-      <c r="D18" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>200</v>
+      <c r="D18" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>154</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="22" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="J18" s="8">
         <v>20000038</v>
@@ -3106,78 +3666,78 @@
       <c r="L18" s="8">
         <v>2000008</v>
       </c>
-      <c r="M18" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="N18" s="13">
-        <v>1</v>
-      </c>
-      <c r="O18" s="13">
-        <v>0</v>
-      </c>
-      <c r="P18" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>0</v>
-      </c>
-      <c r="R18" s="13">
+      <c r="M18" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="N18" s="10">
+        <v>1</v>
+      </c>
+      <c r="O18" s="10">
+        <v>0</v>
+      </c>
+      <c r="P18" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>0</v>
+      </c>
+      <c r="R18" s="10">
         <v>1</v>
       </c>
       <c r="S18" s="9" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U18" s="13">
+        <v>73</v>
+      </c>
+      <c r="U18" s="10">
         <v>12</v>
       </c>
       <c r="V18" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="W18" s="13">
-        <v>0</v>
-      </c>
-      <c r="X18" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="13"/>
+        <v>156</v>
+      </c>
+      <c r="W18" s="10">
+        <v>0</v>
+      </c>
+      <c r="X18" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="10"/>
       <c r="AA18" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB18" s="13"/>
+        <v>157</v>
+      </c>
+      <c r="AB18" s="10"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="9"/>
       <c r="AE18" s="9"/>
-      <c r="AF18" s="13"/>
-      <c r="AG18" s="13"/>
-      <c r="AH18" s="13"/>
+      <c r="AF18" s="10"/>
+      <c r="AG18" s="10"/>
+      <c r="AH18" s="10"/>
       <c r="AI18" s="23" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
     </row>
-    <row r="19" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" ht="20.1" customHeight="1" spans="2:35">
       <c r="C19" s="8">
         <v>2000009</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>178</v>
+      <c r="D19" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>160</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="22" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="J19" s="24" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="K19" s="8">
         <v>17</v>
@@ -3185,75 +3745,75 @@
       <c r="L19" s="8">
         <v>2000009</v>
       </c>
-      <c r="M19" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="N19" s="13">
-        <v>1</v>
-      </c>
-      <c r="O19" s="13">
-        <v>1</v>
-      </c>
-      <c r="P19" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="13">
-        <v>0</v>
-      </c>
-      <c r="R19" s="13">
+      <c r="M19" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="N19" s="10">
+        <v>1</v>
+      </c>
+      <c r="O19" s="10">
+        <v>1</v>
+      </c>
+      <c r="P19" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>0</v>
+      </c>
+      <c r="R19" s="10">
         <v>1</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U19" s="13">
+        <v>73</v>
+      </c>
+      <c r="U19" s="10">
         <v>12</v>
       </c>
       <c r="V19" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="W19" s="13">
-        <v>0</v>
-      </c>
-      <c r="X19" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="13">
+        <v>156</v>
+      </c>
+      <c r="W19" s="10">
+        <v>0</v>
+      </c>
+      <c r="X19" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="10">
         <v>72005013</v>
       </c>
       <c r="AA19" s="8"/>
-      <c r="AB19" s="13"/>
+      <c r="AB19" s="10"/>
       <c r="AC19" s="9"/>
       <c r="AD19" s="9"/>
       <c r="AE19" s="9"/>
-      <c r="AF19" s="13"/>
-      <c r="AG19" s="13"/>
-      <c r="AH19" s="13"/>
+      <c r="AF19" s="10"/>
+      <c r="AG19" s="10"/>
+      <c r="AH19" s="10"/>
       <c r="AI19" s="23" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
     </row>
-    <row r="20" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" ht="20.1" customHeight="1" spans="2:35">
       <c r="C20" s="8">
         <v>2000010</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>179</v>
+      <c r="D20" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>165</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="22" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="8">
@@ -3262,124 +3822,124 @@
       <c r="L20" s="8">
         <v>2000003</v>
       </c>
-      <c r="M20" s="13">
-        <v>0</v>
-      </c>
-      <c r="N20" s="13">
-        <v>1</v>
-      </c>
-      <c r="O20" s="13">
-        <v>1</v>
-      </c>
-      <c r="P20" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="13">
-        <v>0</v>
-      </c>
-      <c r="R20" s="13">
+      <c r="M20" s="10">
+        <v>0</v>
+      </c>
+      <c r="N20" s="10">
+        <v>1</v>
+      </c>
+      <c r="O20" s="10">
+        <v>1</v>
+      </c>
+      <c r="P20" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="10">
+        <v>0</v>
+      </c>
+      <c r="R20" s="10">
         <v>1</v>
       </c>
       <c r="S20" s="9" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U20" s="13">
+        <v>73</v>
+      </c>
+      <c r="U20" s="10">
         <v>1</v>
       </c>
       <c r="V20" s="9"/>
-      <c r="W20" s="13">
+      <c r="W20" s="10">
         <v>2</v>
       </c>
-      <c r="X20" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="13">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="13"/>
+      <c r="X20" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="10"/>
       <c r="AA20" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB20" s="13"/>
+        <v>167</v>
+      </c>
+      <c r="AB20" s="10"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="9"/>
       <c r="AE20" s="9"/>
-      <c r="AF20" s="13"/>
-      <c r="AG20" s="13"/>
-      <c r="AH20" s="13"/>
-      <c r="AI20" s="20" t="s">
-        <v>138</v>
+      <c r="AF20" s="10"/>
+      <c r="AG20" s="10"/>
+      <c r="AH20" s="10"/>
+      <c r="AI20" s="11" t="s">
+        <v>168</v>
       </c>
     </row>
-    <row r="21" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B21"/>
       <c r="C21" s="8">
         <v>2000011</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="22" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="L21" s="13">
+        <v>72</v>
+      </c>
+      <c r="L21" s="10">
         <v>102</v>
       </c>
-      <c r="M21" s="13">
-        <v>0</v>
-      </c>
-      <c r="N21" s="13">
-        <v>1</v>
-      </c>
-      <c r="O21" s="13">
-        <v>0</v>
-      </c>
-      <c r="P21" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="13">
-        <v>0</v>
-      </c>
-      <c r="R21" s="13">
+      <c r="M21" s="10">
+        <v>0</v>
+      </c>
+      <c r="N21" s="10">
+        <v>1</v>
+      </c>
+      <c r="O21" s="10">
+        <v>0</v>
+      </c>
+      <c r="P21" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>0</v>
+      </c>
+      <c r="R21" s="10">
         <v>1</v>
       </c>
       <c r="S21" s="9" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="U21" s="13">
+        <v>74</v>
+      </c>
+      <c r="U21" s="10">
         <v>10</v>
       </c>
       <c r="V21" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="W21" s="13">
-        <v>0</v>
-      </c>
-      <c r="X21" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="13">
+        <v>74</v>
+      </c>
+      <c r="W21" s="10">
+        <v>0</v>
+      </c>
+      <c r="X21" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="10">
         <v>0</v>
       </c>
       <c r="AA21" s="9"/>
@@ -3387,35 +3947,35 @@
       <c r="AC21" s="9"/>
       <c r="AD21" s="9"/>
       <c r="AE21" s="9"/>
-      <c r="AF21" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="13">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="20" t="s">
-        <v>143</v>
+      <c r="AF21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="11" t="s">
+        <v>174</v>
       </c>
     </row>
-    <row r="22" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B22"/>
       <c r="C22" s="8">
         <v>2100001</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="22" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="8">
@@ -3424,70 +3984,70 @@
       <c r="L22" s="8">
         <v>100001</v>
       </c>
-      <c r="M22" s="13">
-        <v>0</v>
-      </c>
-      <c r="N22" s="13">
-        <v>0</v>
-      </c>
-      <c r="O22" s="13">
-        <v>1</v>
-      </c>
-      <c r="P22" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>0</v>
-      </c>
-      <c r="R22" s="13">
+      <c r="M22" s="10">
+        <v>0</v>
+      </c>
+      <c r="N22" s="10">
+        <v>0</v>
+      </c>
+      <c r="O22" s="10">
+        <v>1</v>
+      </c>
+      <c r="P22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>0</v>
+      </c>
+      <c r="R22" s="10">
         <v>1</v>
       </c>
       <c r="S22" s="9" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U22" s="13">
+        <v>73</v>
+      </c>
+      <c r="U22" s="10">
         <v>1</v>
       </c>
       <c r="V22" s="9"/>
-      <c r="W22" s="13">
-        <v>1</v>
-      </c>
-      <c r="X22" s="13">
+      <c r="W22" s="10">
+        <v>1</v>
+      </c>
+      <c r="X22" s="10">
         <v>5</v>
       </c>
-      <c r="Y22" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="13"/>
+      <c r="Y22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="10"/>
       <c r="AA22" s="8"/>
-      <c r="AB22" s="13"/>
+      <c r="AB22" s="10"/>
       <c r="AC22" s="9"/>
       <c r="AD22" s="9"/>
       <c r="AE22" s="9"/>
-      <c r="AF22" s="13"/>
-      <c r="AG22" s="13"/>
-      <c r="AH22" s="13"/>
-      <c r="AI22" s="20"/>
+      <c r="AF22" s="10"/>
+      <c r="AG22" s="10"/>
+      <c r="AH22" s="10"/>
+      <c r="AI22" s="11"/>
     </row>
-    <row r="23" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B23"/>
       <c r="C23" s="8">
         <v>2100002</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="22" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="J23" s="8"/>
       <c r="K23" s="8">
@@ -3496,70 +4056,70 @@
       <c r="L23" s="8">
         <v>100001</v>
       </c>
-      <c r="M23" s="13">
-        <v>0</v>
-      </c>
-      <c r="N23" s="13">
-        <v>0</v>
-      </c>
-      <c r="O23" s="13">
-        <v>1</v>
-      </c>
-      <c r="P23" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="13">
-        <v>0</v>
-      </c>
-      <c r="R23" s="13">
+      <c r="M23" s="10">
+        <v>0</v>
+      </c>
+      <c r="N23" s="10">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10">
+        <v>1</v>
+      </c>
+      <c r="P23" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>0</v>
+      </c>
+      <c r="R23" s="10">
         <v>1</v>
       </c>
       <c r="S23" s="9" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U23" s="13">
+        <v>73</v>
+      </c>
+      <c r="U23" s="10">
         <v>1</v>
       </c>
       <c r="V23" s="9"/>
-      <c r="W23" s="13">
-        <v>1</v>
-      </c>
-      <c r="X23" s="13">
+      <c r="W23" s="10">
+        <v>1</v>
+      </c>
+      <c r="X23" s="10">
         <v>10</v>
       </c>
-      <c r="Y23" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="13"/>
+      <c r="Y23" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="10"/>
       <c r="AA23" s="8"/>
-      <c r="AB23" s="13"/>
+      <c r="AB23" s="10"/>
       <c r="AC23" s="9"/>
       <c r="AD23" s="9"/>
       <c r="AE23" s="9"/>
-      <c r="AF23" s="13"/>
-      <c r="AG23" s="13"/>
-      <c r="AH23" s="13"/>
-      <c r="AI23" s="20"/>
+      <c r="AF23" s="10"/>
+      <c r="AG23" s="10"/>
+      <c r="AH23" s="10"/>
+      <c r="AI23" s="11"/>
     </row>
-    <row r="24" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B24"/>
       <c r="C24" s="8">
         <v>2200001</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="22" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="J24" s="8"/>
       <c r="K24" s="8">
@@ -3568,72 +4128,72 @@
       <c r="L24" s="8">
         <v>10007</v>
       </c>
-      <c r="M24" s="13">
-        <v>0</v>
-      </c>
-      <c r="N24" s="13">
-        <v>0</v>
-      </c>
-      <c r="O24" s="13">
-        <v>1</v>
-      </c>
-      <c r="P24" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="13">
-        <v>0</v>
-      </c>
-      <c r="R24" s="13">
+      <c r="M24" s="10">
+        <v>0</v>
+      </c>
+      <c r="N24" s="10">
+        <v>0</v>
+      </c>
+      <c r="O24" s="10">
+        <v>1</v>
+      </c>
+      <c r="P24" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>0</v>
+      </c>
+      <c r="R24" s="10">
         <v>1</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U24" s="13">
+        <v>73</v>
+      </c>
+      <c r="U24" s="10">
         <v>1</v>
       </c>
       <c r="V24" s="9"/>
-      <c r="W24" s="13">
-        <v>1</v>
-      </c>
-      <c r="X24" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="13"/>
+      <c r="W24" s="10">
+        <v>1</v>
+      </c>
+      <c r="X24" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="10"/>
       <c r="AA24" s="9"/>
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="9"/>
       <c r="AE24" s="9"/>
-      <c r="AF24" s="13"/>
-      <c r="AG24" s="13"/>
-      <c r="AH24" s="13"/>
-      <c r="AI24" s="20"/>
+      <c r="AF24" s="10"/>
+      <c r="AG24" s="10"/>
+      <c r="AH24" s="10"/>
+      <c r="AI24" s="11"/>
     </row>
-    <row r="25" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" ht="20.1" customHeight="1" spans="2:35">
       <c r="C25" s="8">
         <v>3000001</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="22" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="K25" s="8">
         <v>12</v>
@@ -3641,78 +4201,78 @@
       <c r="L25" s="8">
         <v>201</v>
       </c>
-      <c r="M25" s="13">
-        <v>0</v>
-      </c>
-      <c r="N25" s="13">
-        <v>1</v>
-      </c>
-      <c r="O25" s="13">
-        <v>0</v>
-      </c>
-      <c r="P25" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="13">
-        <v>0</v>
-      </c>
-      <c r="R25" s="13">
+      <c r="M25" s="10">
+        <v>0</v>
+      </c>
+      <c r="N25" s="10">
+        <v>1</v>
+      </c>
+      <c r="O25" s="10">
+        <v>0</v>
+      </c>
+      <c r="P25" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>0</v>
+      </c>
+      <c r="R25" s="10">
         <v>1</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U25" s="13">
+        <v>73</v>
+      </c>
+      <c r="U25" s="10">
         <v>10</v>
       </c>
       <c r="V25" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="W25" s="13">
+        <v>186</v>
+      </c>
+      <c r="W25" s="10">
         <v>40</v>
       </c>
-      <c r="X25" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="13"/>
+      <c r="X25" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="10"/>
       <c r="AA25" s="8"/>
       <c r="AB25" s="25" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="AC25" s="9"/>
       <c r="AD25" s="9"/>
       <c r="AE25" s="9"/>
-      <c r="AF25" s="13"/>
-      <c r="AG25" s="13"/>
-      <c r="AH25" s="13"/>
-      <c r="AI25" s="20" t="s">
-        <v>138</v>
+      <c r="AF25" s="10"/>
+      <c r="AG25" s="10"/>
+      <c r="AH25" s="10"/>
+      <c r="AI25" s="11" t="s">
+        <v>168</v>
       </c>
     </row>
-    <row r="26" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" ht="20.1" customHeight="1" spans="2:35">
       <c r="C26" s="8">
         <v>3000002</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="22" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="K26" s="8">
         <v>12</v>
@@ -3720,76 +4280,76 @@
       <c r="L26" s="8">
         <v>201</v>
       </c>
-      <c r="M26" s="13">
-        <v>0</v>
-      </c>
-      <c r="N26" s="13">
-        <v>1</v>
-      </c>
-      <c r="O26" s="13">
-        <v>0</v>
-      </c>
-      <c r="P26" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="13">
-        <v>0</v>
-      </c>
-      <c r="R26" s="13">
+      <c r="M26" s="10">
+        <v>0</v>
+      </c>
+      <c r="N26" s="10">
+        <v>1</v>
+      </c>
+      <c r="O26" s="10">
+        <v>0</v>
+      </c>
+      <c r="P26" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="10">
+        <v>0</v>
+      </c>
+      <c r="R26" s="10">
         <v>1</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U26" s="13">
+        <v>73</v>
+      </c>
+      <c r="U26" s="10">
         <v>30</v>
       </c>
       <c r="V26" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="W26" s="13">
+        <v>190</v>
+      </c>
+      <c r="W26" s="10">
         <v>40</v>
       </c>
-      <c r="X26" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="13"/>
+      <c r="X26" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="10"/>
       <c r="AA26" s="8"/>
       <c r="AB26" s="25" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="AC26" s="9"/>
       <c r="AD26" s="9"/>
       <c r="AE26" s="9"/>
-      <c r="AF26" s="13"/>
-      <c r="AG26" s="13"/>
-      <c r="AH26" s="13"/>
-      <c r="AI26" s="20" t="s">
-        <v>138</v>
+      <c r="AF26" s="10"/>
+      <c r="AG26" s="10"/>
+      <c r="AH26" s="10"/>
+      <c r="AI26" s="11" t="s">
+        <v>168</v>
       </c>
     </row>
-    <row r="27" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B27"/>
       <c r="C27" s="8">
         <v>4000001</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="22" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="8">
@@ -3801,69 +4361,69 @@
       <c r="M27" s="8">
         <v>2000004</v>
       </c>
-      <c r="N27" s="13">
-        <v>0</v>
-      </c>
-      <c r="O27" s="13">
-        <v>1</v>
-      </c>
-      <c r="P27" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="13">
-        <v>0</v>
-      </c>
-      <c r="R27" s="13">
+      <c r="N27" s="10">
+        <v>0</v>
+      </c>
+      <c r="O27" s="10">
+        <v>1</v>
+      </c>
+      <c r="P27" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="10">
+        <v>0</v>
+      </c>
+      <c r="R27" s="10">
         <v>1</v>
       </c>
       <c r="S27" s="9" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U27" s="13">
+        <v>73</v>
+      </c>
+      <c r="U27" s="10">
         <v>10</v>
       </c>
       <c r="V27" s="9"/>
-      <c r="W27" s="13">
-        <v>0</v>
-      </c>
-      <c r="X27" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="13"/>
+      <c r="W27" s="10">
+        <v>0</v>
+      </c>
+      <c r="X27" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="10"/>
       <c r="AA27" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="AB27" s="13"/>
+        <v>152</v>
+      </c>
+      <c r="AB27" s="10"/>
       <c r="AC27" s="9"/>
       <c r="AD27" s="9"/>
       <c r="AE27" s="9"/>
-      <c r="AF27" s="13"/>
-      <c r="AG27" s="13"/>
-      <c r="AH27" s="13"/>
-      <c r="AI27" s="20"/>
+      <c r="AF27" s="10"/>
+      <c r="AG27" s="10"/>
+      <c r="AH27" s="10"/>
+      <c r="AI27" s="11"/>
     </row>
-    <row r="28" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B28"/>
       <c r="C28" s="8">
         <v>5000001</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="22" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="J28" s="8"/>
       <c r="K28" s="8">
@@ -3875,68 +4435,68 @@
       <c r="M28" s="8">
         <v>2000004</v>
       </c>
-      <c r="N28" s="13">
-        <v>0</v>
-      </c>
-      <c r="O28" s="13">
-        <v>1</v>
-      </c>
-      <c r="P28" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="13">
-        <v>0</v>
-      </c>
-      <c r="R28" s="13">
+      <c r="N28" s="10">
+        <v>0</v>
+      </c>
+      <c r="O28" s="10">
+        <v>1</v>
+      </c>
+      <c r="P28" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="10">
+        <v>0</v>
+      </c>
+      <c r="R28" s="10">
         <v>1</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U28" s="13">
+        <v>73</v>
+      </c>
+      <c r="U28" s="10">
         <v>10</v>
       </c>
       <c r="V28" s="9"/>
-      <c r="W28" s="13">
-        <v>0</v>
-      </c>
-      <c r="X28" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="13"/>
+      <c r="W28" s="10">
+        <v>0</v>
+      </c>
+      <c r="X28" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="10"/>
       <c r="AA28" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="AB28" s="13"/>
+        <v>152</v>
+      </c>
+      <c r="AB28" s="10"/>
       <c r="AC28" s="9"/>
       <c r="AD28" s="9"/>
       <c r="AE28" s="9"/>
-      <c r="AF28" s="13"/>
-      <c r="AG28" s="13"/>
-      <c r="AH28" s="13"/>
-      <c r="AI28" s="20"/>
+      <c r="AF28" s="10"/>
+      <c r="AG28" s="10"/>
+      <c r="AH28" s="10"/>
+      <c r="AI28" s="11"/>
     </row>
-    <row r="29" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" ht="20.1" customHeight="1" spans="2:35">
       <c r="C29" s="8">
         <v>6000001</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>187</v>
+      <c r="D29" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>195</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="22" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="J29" s="8"/>
       <c r="K29" s="8">
@@ -3945,226 +4505,226 @@
       <c r="L29" s="8">
         <v>2000006</v>
       </c>
-      <c r="M29" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="N29" s="13">
-        <v>1</v>
-      </c>
-      <c r="O29" s="13">
-        <v>1</v>
-      </c>
-      <c r="P29" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="13">
-        <v>0</v>
-      </c>
-      <c r="R29" s="13">
+      <c r="M29" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="N29" s="10">
+        <v>1</v>
+      </c>
+      <c r="O29" s="10">
+        <v>1</v>
+      </c>
+      <c r="P29" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="10">
+        <v>0</v>
+      </c>
+      <c r="R29" s="10">
         <v>1</v>
       </c>
       <c r="S29" s="9" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U29" s="13">
+        <v>73</v>
+      </c>
+      <c r="U29" s="10">
         <v>12</v>
       </c>
       <c r="V29" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="W29" s="13">
+        <v>156</v>
+      </c>
+      <c r="W29" s="10">
         <v>100</v>
       </c>
-      <c r="X29" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="13"/>
+      <c r="X29" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="10"/>
       <c r="AA29" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB29" s="13"/>
+        <v>197</v>
+      </c>
+      <c r="AB29" s="10"/>
       <c r="AC29" s="9"/>
       <c r="AD29" s="9"/>
       <c r="AE29" s="9"/>
-      <c r="AF29" s="13"/>
-      <c r="AG29" s="13"/>
-      <c r="AH29" s="13"/>
-      <c r="AI29" s="20" t="s">
-        <v>160</v>
+      <c r="AF29" s="10"/>
+      <c r="AG29" s="10"/>
+      <c r="AH29" s="10"/>
+      <c r="AI29" s="11" t="s">
+        <v>198</v>
       </c>
     </row>
-    <row r="30" spans="2:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" s="3" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B30"/>
-      <c r="C30" s="11">
+      <c r="C30" s="18">
         <v>6000002</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30" s="12" t="s">
+      <c r="D30" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18">
+        <v>22</v>
+      </c>
+      <c r="L30" s="18">
+        <v>2000011</v>
+      </c>
+      <c r="M30" s="20">
+        <v>0</v>
+      </c>
+      <c r="N30" s="20">
+        <v>0</v>
+      </c>
+      <c r="O30" s="20">
+        <v>1</v>
+      </c>
+      <c r="P30" s="20">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="20">
+        <v>0</v>
+      </c>
+      <c r="R30" s="20">
+        <v>1</v>
+      </c>
+      <c r="S30" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="T30" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="U30" s="20">
+        <v>1</v>
+      </c>
+      <c r="V30" s="19"/>
+      <c r="W30" s="20">
+        <v>0</v>
+      </c>
+      <c r="X30" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="20"/>
+      <c r="AA30" s="18"/>
+      <c r="AB30" s="20">
+        <v>100101</v>
+      </c>
+      <c r="AC30" s="19"/>
+      <c r="AD30" s="19"/>
+      <c r="AE30" s="19"/>
+      <c r="AF30" s="20"/>
+      <c r="AG30" s="20"/>
+      <c r="AH30" s="20"/>
+      <c r="AI30" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11">
-        <v>22</v>
-      </c>
-      <c r="L30" s="11">
+    </row>
+    <row r="31" s="3" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
+      <c r="B31"/>
+      <c r="C31" s="18">
+        <v>6000003</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18">
+        <v>23</v>
+      </c>
+      <c r="L31" s="18">
         <v>2000011</v>
       </c>
-      <c r="M30" s="18">
-        <v>0</v>
-      </c>
-      <c r="N30" s="18">
-        <v>0</v>
-      </c>
-      <c r="O30" s="18">
-        <v>1</v>
-      </c>
-      <c r="P30" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="18">
-        <v>0</v>
-      </c>
-      <c r="R30" s="18">
-        <v>1</v>
-      </c>
-      <c r="S30" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="T30" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="U30" s="18">
-        <v>1</v>
-      </c>
-      <c r="V30" s="12"/>
-      <c r="W30" s="18">
-        <v>0</v>
-      </c>
-      <c r="X30" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="18">
-        <v>1</v>
-      </c>
-      <c r="Z30" s="18"/>
-      <c r="AA30" s="11"/>
-      <c r="AB30" s="18">
-        <v>100101</v>
-      </c>
-      <c r="AC30" s="12"/>
-      <c r="AD30" s="12"/>
-      <c r="AE30" s="12"/>
-      <c r="AF30" s="18"/>
-      <c r="AG30" s="18"/>
-      <c r="AH30" s="18"/>
-      <c r="AI30" s="21" t="s">
-        <v>160</v>
+      <c r="M31" s="20">
+        <v>0</v>
+      </c>
+      <c r="N31" s="20">
+        <v>0</v>
+      </c>
+      <c r="O31" s="20">
+        <v>1</v>
+      </c>
+      <c r="P31" s="20">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="20">
+        <v>0</v>
+      </c>
+      <c r="R31" s="20">
+        <v>1</v>
+      </c>
+      <c r="S31" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="T31" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="U31" s="20">
+        <v>1</v>
+      </c>
+      <c r="V31" s="19"/>
+      <c r="W31" s="20">
+        <v>0</v>
+      </c>
+      <c r="X31" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="20"/>
+      <c r="AA31" s="18"/>
+      <c r="AB31" s="20"/>
+      <c r="AC31" s="19"/>
+      <c r="AD31" s="19"/>
+      <c r="AE31" s="19"/>
+      <c r="AF31" s="20"/>
+      <c r="AG31" s="20"/>
+      <c r="AH31" s="20"/>
+      <c r="AI31" s="21" t="s">
+        <v>198</v>
       </c>
     </row>
-    <row r="31" spans="2:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31"/>
-      <c r="C31" s="11">
-        <v>6000003</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11">
-        <v>23</v>
-      </c>
-      <c r="L31" s="11">
-        <v>2000011</v>
-      </c>
-      <c r="M31" s="18">
-        <v>0</v>
-      </c>
-      <c r="N31" s="18">
-        <v>0</v>
-      </c>
-      <c r="O31" s="18">
-        <v>1</v>
-      </c>
-      <c r="P31" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="18">
-        <v>0</v>
-      </c>
-      <c r="R31" s="18">
-        <v>1</v>
-      </c>
-      <c r="S31" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="T31" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="U31" s="18">
-        <v>1</v>
-      </c>
-      <c r="V31" s="12"/>
-      <c r="W31" s="18">
-        <v>0</v>
-      </c>
-      <c r="X31" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="18">
-        <v>1</v>
-      </c>
-      <c r="Z31" s="18"/>
-      <c r="AA31" s="11"/>
-      <c r="AB31" s="18"/>
-      <c r="AC31" s="12"/>
-      <c r="AD31" s="12"/>
-      <c r="AE31" s="12"/>
-      <c r="AF31" s="18"/>
-      <c r="AG31" s="18"/>
-      <c r="AH31" s="18"/>
-      <c r="AI31" s="21" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="32" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B32"/>
       <c r="C32" s="8">
         <v>7000001</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="22" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="8">
@@ -4173,72 +4733,72 @@
       <c r="L32" s="8">
         <v>2000004</v>
       </c>
-      <c r="M32" s="13">
-        <v>0</v>
-      </c>
-      <c r="N32" s="13">
-        <v>0</v>
-      </c>
-      <c r="O32" s="13">
-        <v>1</v>
-      </c>
-      <c r="P32" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="13">
-        <v>0</v>
-      </c>
-      <c r="R32" s="13">
+      <c r="M32" s="10">
+        <v>0</v>
+      </c>
+      <c r="N32" s="10">
+        <v>0</v>
+      </c>
+      <c r="O32" s="10">
+        <v>1</v>
+      </c>
+      <c r="P32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>0</v>
+      </c>
+      <c r="R32" s="10">
         <v>1</v>
       </c>
       <c r="S32" s="9" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U32" s="13">
+        <v>73</v>
+      </c>
+      <c r="U32" s="10">
         <v>1</v>
       </c>
       <c r="V32" s="9"/>
-      <c r="W32" s="13">
-        <v>0</v>
-      </c>
-      <c r="X32" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="13"/>
+      <c r="W32" s="10">
+        <v>0</v>
+      </c>
+      <c r="X32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="10"/>
       <c r="AA32" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="AB32" s="13"/>
+        <v>152</v>
+      </c>
+      <c r="AB32" s="10"/>
       <c r="AC32" s="9"/>
       <c r="AD32" s="9"/>
       <c r="AE32" s="9"/>
-      <c r="AF32" s="13"/>
-      <c r="AG32" s="13"/>
-      <c r="AH32" s="13"/>
-      <c r="AI32" s="20"/>
+      <c r="AF32" s="10"/>
+      <c r="AG32" s="10"/>
+      <c r="AH32" s="10"/>
+      <c r="AI32" s="11"/>
     </row>
-    <row r="33" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B33"/>
       <c r="C33" s="8">
         <v>8000001</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="22" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8">
@@ -4247,72 +4807,72 @@
       <c r="L33" s="8">
         <v>2000010</v>
       </c>
-      <c r="M33" s="13">
-        <v>0</v>
-      </c>
-      <c r="N33" s="13">
-        <v>0</v>
-      </c>
-      <c r="O33" s="13">
-        <v>1</v>
-      </c>
-      <c r="P33" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="13">
-        <v>0</v>
-      </c>
-      <c r="R33" s="13">
+      <c r="M33" s="10">
+        <v>0</v>
+      </c>
+      <c r="N33" s="10">
+        <v>0</v>
+      </c>
+      <c r="O33" s="10">
+        <v>1</v>
+      </c>
+      <c r="P33" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="10">
+        <v>0</v>
+      </c>
+      <c r="R33" s="10">
         <v>1</v>
       </c>
       <c r="S33" s="9" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U33" s="13">
+        <v>73</v>
+      </c>
+      <c r="U33" s="10">
         <v>1</v>
       </c>
       <c r="V33" s="9"/>
-      <c r="W33" s="13">
-        <v>0</v>
-      </c>
-      <c r="X33" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="13"/>
+      <c r="W33" s="10">
+        <v>0</v>
+      </c>
+      <c r="X33" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="10"/>
       <c r="AA33" s="8"/>
-      <c r="AB33" s="13"/>
+      <c r="AB33" s="10"/>
       <c r="AC33" s="9"/>
       <c r="AD33" s="9"/>
       <c r="AE33" s="9"/>
-      <c r="AF33" s="13"/>
-      <c r="AG33" s="13"/>
-      <c r="AH33" s="13"/>
-      <c r="AI33" s="20" t="s">
-        <v>160</v>
+      <c r="AF33" s="10"/>
+      <c r="AG33" s="10"/>
+      <c r="AH33" s="10"/>
+      <c r="AI33" s="11" t="s">
+        <v>198</v>
       </c>
     </row>
-    <row r="34" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B34"/>
       <c r="C34" s="8">
         <v>2400001</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="22" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="8">
@@ -4321,70 +4881,70 @@
       <c r="L34" s="8">
         <v>100001</v>
       </c>
-      <c r="M34" s="13">
-        <v>0</v>
-      </c>
-      <c r="N34" s="13">
-        <v>0</v>
-      </c>
-      <c r="O34" s="13">
-        <v>1</v>
-      </c>
-      <c r="P34" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="13">
-        <v>0</v>
-      </c>
-      <c r="R34" s="13">
+      <c r="M34" s="10">
+        <v>0</v>
+      </c>
+      <c r="N34" s="10">
+        <v>0</v>
+      </c>
+      <c r="O34" s="10">
+        <v>1</v>
+      </c>
+      <c r="P34" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="10">
+        <v>0</v>
+      </c>
+      <c r="R34" s="10">
         <v>1</v>
       </c>
       <c r="S34" s="9" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U34" s="13">
+        <v>73</v>
+      </c>
+      <c r="U34" s="10">
         <v>1</v>
       </c>
       <c r="V34" s="9"/>
-      <c r="W34" s="13">
-        <v>1</v>
-      </c>
-      <c r="X34" s="13">
+      <c r="W34" s="10">
+        <v>1</v>
+      </c>
+      <c r="X34" s="10">
         <v>10</v>
       </c>
-      <c r="Y34" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="13"/>
+      <c r="Y34" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="10"/>
       <c r="AA34" s="8"/>
-      <c r="AB34" s="13"/>
+      <c r="AB34" s="10"/>
       <c r="AC34" s="9"/>
       <c r="AD34" s="9"/>
       <c r="AE34" s="9"/>
-      <c r="AF34" s="13"/>
-      <c r="AG34" s="13"/>
-      <c r="AH34" s="13"/>
-      <c r="AI34" s="20"/>
+      <c r="AF34" s="10"/>
+      <c r="AG34" s="10"/>
+      <c r="AH34" s="10"/>
+      <c r="AI34" s="11"/>
     </row>
-    <row r="35" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:35">
       <c r="B35"/>
       <c r="C35" s="8">
         <v>2500001</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>167</v>
+        <v>210</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="22" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8">
@@ -4393,71 +4953,71 @@
       <c r="L35" s="8">
         <v>2000004</v>
       </c>
-      <c r="M35" s="13">
-        <v>0</v>
-      </c>
-      <c r="N35" s="13">
-        <v>0</v>
-      </c>
-      <c r="O35" s="13">
-        <v>1</v>
-      </c>
-      <c r="P35" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="13">
-        <v>0</v>
-      </c>
-      <c r="R35" s="13">
+      <c r="M35" s="10">
+        <v>0</v>
+      </c>
+      <c r="N35" s="10">
+        <v>0</v>
+      </c>
+      <c r="O35" s="10">
+        <v>1</v>
+      </c>
+      <c r="P35" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="10">
+        <v>0</v>
+      </c>
+      <c r="R35" s="10">
         <v>1</v>
       </c>
       <c r="S35" s="9" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U35" s="13">
+        <v>73</v>
+      </c>
+      <c r="U35" s="10">
         <v>1</v>
       </c>
       <c r="V35" s="9"/>
-      <c r="W35" s="13">
-        <v>0</v>
-      </c>
-      <c r="X35" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="13"/>
+      <c r="W35" s="10">
+        <v>0</v>
+      </c>
+      <c r="X35" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="10"/>
       <c r="AA35" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="AB35" s="13"/>
+        <v>152</v>
+      </c>
+      <c r="AB35" s="10"/>
       <c r="AC35" s="9"/>
       <c r="AD35" s="9"/>
       <c r="AE35" s="9"/>
-      <c r="AF35" s="13"/>
-      <c r="AG35" s="13"/>
-      <c r="AH35" s="13"/>
-      <c r="AI35" s="20"/>
+      <c r="AF35" s="10"/>
+      <c r="AG35" s="10"/>
+      <c r="AH35" s="10"/>
+      <c r="AI35" s="11"/>
     </row>
-    <row r="36" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" ht="20.1" customHeight="1" spans="2:35">
       <c r="C36" s="8">
         <v>2600001</v>
       </c>
-      <c r="D36" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>192</v>
+      <c r="D36" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>213</v>
       </c>
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
       <c r="I36" s="22" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8">
@@ -4466,64 +5026,64 @@
       <c r="L36" s="8">
         <v>2000003</v>
       </c>
-      <c r="M36" s="13">
-        <v>0</v>
-      </c>
-      <c r="N36" s="13">
-        <v>1</v>
-      </c>
-      <c r="O36" s="13">
-        <v>1</v>
-      </c>
-      <c r="P36" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="13">
-        <v>0</v>
-      </c>
-      <c r="R36" s="13">
+      <c r="M36" s="10">
+        <v>0</v>
+      </c>
+      <c r="N36" s="10">
+        <v>1</v>
+      </c>
+      <c r="O36" s="10">
+        <v>1</v>
+      </c>
+      <c r="P36" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="10">
+        <v>0</v>
+      </c>
+      <c r="R36" s="10">
         <v>1</v>
       </c>
       <c r="S36" s="9" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="T36" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="U36" s="13">
+        <v>73</v>
+      </c>
+      <c r="U36" s="10">
         <v>1</v>
       </c>
       <c r="V36" s="9"/>
-      <c r="W36" s="13">
+      <c r="W36" s="10">
         <v>2</v>
       </c>
-      <c r="X36" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="13">
-        <v>1</v>
-      </c>
-      <c r="Z36" s="13"/>
+      <c r="X36" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="10"/>
       <c r="AA36" s="8"/>
-      <c r="AB36" s="13"/>
+      <c r="AB36" s="10"/>
       <c r="AC36" s="9"/>
       <c r="AD36" s="9"/>
       <c r="AE36" s="9"/>
-      <c r="AF36" s="13"/>
-      <c r="AG36" s="13"/>
-      <c r="AH36" s="13"/>
-      <c r="AI36" s="20" t="s">
-        <v>138</v>
+      <c r="AF36" s="10"/>
+      <c r="AG36" s="10"/>
+      <c r="AH36" s="10"/>
+      <c r="AI36" s="11" t="s">
+        <v>168</v>
       </c>
     </row>
-    <row r="37" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="37" ht="20.1" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Excel/SceneConfig.xlsx
+++ b/Excel/SceneConfig.xlsx
@@ -485,13 +485,13 @@
     <t>Main City</t>
   </si>
   <si>
-    <t>-4000,-0,8,2983,10000</t>
+    <t>-1000,0,0,10000</t>
   </si>
   <si>
     <t>-1000,0,0</t>
   </si>
   <si>
-    <t>20000001,20000002,20000003,20000004,20000006,20000009,20000010,20000011,20000012,20000013,20000014,20000015,20000016,20000017,20000018,20000019,20000020,20000021,20000022,20000023,20000024,20000025,20000026,20000027,20000028,20000029,20000030,20000031,20000032,20000033,20000036,20000037,30000011,20000039,20000040,20000041,20000042,20000043,20000044</t>
+    <t>20000001,20000002,20000003,20000004,20000006,20000009,20000010,20000011,20000012,20000013,20000014,20000015,20000016,20000017,20000018,20000019,20000020,20000021,20000022,20000023,20000024,20000025,20000026,20000027,20000028,20000029,20000030,20000031,20000032,20000033,20000036,20000037,20000039,20000040,20000041,20000042,20000043,20000044,30000011</t>
   </si>
   <si>
     <t>3</t>
@@ -1044,7 +1044,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1054,13 +1054,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1649,138 +1642,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1793,12 +1786,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1819,13 +1812,13 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2614,7 +2607,7 @@
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="22" t="s">
         <v>69</v>
       </c>
       <c r="I6" s="22" t="s">
